--- a/lab1/lab1.xlsx
+++ b/lab1/lab1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\study\3course\2sem\PO\lab1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\study\3course\2sem\PO\PO-labs\lab1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A659CBFF-4453-4A51-8D8E-25B327A0BA20}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFF432F-8081-4FA8-93CE-AD01F2F50C85}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
   <si>
     <t>Matrix Size     Threads Time (seconds)  Correct?</t>
   </si>
@@ -157,6 +157,9 @@
   </si>
   <si>
     <t>Time</t>
+  </si>
+  <si>
+    <t>/</t>
   </si>
 </sst>
 </file>
@@ -5180,7 +5183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.7109375" customWidth="1"/>
@@ -5691,12 +5694,17 @@
         <v>4.0424610000000003</v>
       </c>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C65" s="1">
         <v>192</v>
       </c>
       <c r="D65" s="1">
         <v>4.1640730000000001</v>
+      </c>
+    </row>
+    <row r="72" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="F72" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
